--- a/outputs/validation/comparison_manual_model_42.xlsx
+++ b/outputs/validation/comparison_manual_model_42.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,34 +1064,34 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="H14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" t="n">
         <v>36</v>
       </c>
       <c r="J14" t="n">
-        <v>0.959</v>
+        <v>0.98</v>
       </c>
       <c r="K14" t="n">
-        <v>0.973</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0.973</v>
       </c>
       <c r="M14" t="n">
-        <v>0.973</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="15">
@@ -2242,31 +2242,31 @@
         <v>0.49</v>
       </c>
       <c r="E39" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="F39" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I39" t="n">
         <v>36</v>
       </c>
       <c r="J39" t="n">
-        <v>0.959</v>
+        <v>0.98</v>
       </c>
       <c r="K39" t="n">
-        <v>0.973</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0.973</v>
       </c>
       <c r="M39" t="n">
-        <v>0.973</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="40">
@@ -2940,17 +2940,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D54" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="F54" t="n">
         <v>0.84</v>
-      </c>
-      <c r="E54" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.86</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2959,19 +2959,19 @@
         <v>37</v>
       </c>
       <c r="I54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J54" t="n">
-        <v>0.959</v>
+        <v>0.878</v>
       </c>
       <c r="K54" t="n">
-        <v>0.973</v>
+        <v>0.919</v>
       </c>
       <c r="L54" t="n">
-        <v>0.973</v>
+        <v>0.919</v>
       </c>
       <c r="M54" t="n">
-        <v>0.973</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="55">
@@ -2987,38 +2987,38 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="E55" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I55" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J55" t="n">
-        <v>0.878</v>
+        <v>0.918</v>
       </c>
       <c r="K55" t="n">
-        <v>0.919</v>
+        <v>0.923</v>
       </c>
       <c r="L55" t="n">
-        <v>0.919</v>
+        <v>0.973</v>
       </c>
       <c r="M55" t="n">
-        <v>0.919</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="56">
@@ -3034,38 +3034,38 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="E56" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="F56" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I56" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J56" t="n">
-        <v>0.918</v>
+        <v>0.755</v>
       </c>
       <c r="K56" t="n">
-        <v>0.923</v>
+        <v>0.755</v>
       </c>
       <c r="L56" t="n">
-        <v>0.973</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.947</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="57">
@@ -3081,84 +3081,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="E57" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="F57" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I57" t="n">
         <v>37</v>
       </c>
       <c r="J57" t="n">
-        <v>0.755</v>
+        <v>0.918</v>
       </c>
       <c r="K57" t="n">
-        <v>0.755</v>
+        <v>0.902</v>
       </c>
       <c r="L57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>populism_all_statements_vs_all_models</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>41</v>
-      </c>
-      <c r="I58" t="n">
-        <v>37</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="n">
         <v>0.949</v>
       </c>
     </row>
